--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test Coding\cek nilai tka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFA12AB-C522-492B-87A5-70C9C83C7232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80F8FF0-400E-4765-9D94-07D783D54077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1876,7 +1876,7 @@
     <t>SURABAYA, 26 September 2010</t>
   </si>
   <si>
-    <t>Alief Adam</t>
+    <t>Alief Adammmmmmm</t>
   </si>
 </sst>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test Coding\cek nilai tka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80F8FF0-400E-4765-9D94-07D783D54077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7094660-FE8D-4AB3-8098-12167F3D0C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1876,7 +1876,7 @@
     <t>SURABAYA, 26 September 2010</t>
   </si>
   <si>
-    <t>Alief Adammmmmmm</t>
+    <t>Alief Adammmmmmm sssssss</t>
   </si>
 </sst>
 </file>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test Coding\cek nilai tka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7094660-FE8D-4AB3-8098-12167F3D0C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893DA742-9D53-412A-8853-F01F326D471D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="608">
   <si>
     <t>NISN</t>
   </si>
@@ -1877,6 +1877,9 @@
   </si>
   <si>
     <t>Alief Adammmmmmm sssssss</t>
+  </si>
+  <si>
+    <t>RIDZ</t>
   </si>
 </sst>
 </file>
@@ -6113,12 +6116,24 @@
       </c>
     </row>
     <row r="198" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
-      <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
-      <c r="C198" s="3"/>
-      <c r="D198" s="3"/>
-      <c r="E198" s="3"/>
-      <c r="F198" s="3"/>
+      <c r="A198" s="3">
+        <v>12345</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="199" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
